--- a/Topp100_CO2_2023.xlsx
+++ b/Topp100_CO2_2023.xlsx
@@ -816,7 +816,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Ferrosilisium?</t>
+          <t>Ferrosilisium</t>
         </is>
       </c>
     </row>

--- a/Topp100_CO2_2023.xlsx
+++ b/Topp100_CO2_2023.xlsx
@@ -1457,7 +1457,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Kalk?</t>
+          <t>Kalk</t>
         </is>
       </c>
     </row>

--- a/Topp100_CO2_2023.xlsx
+++ b/Topp100_CO2_2023.xlsx
@@ -957,7 +957,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>titan</t>
+          <t>titanslagg og råjern</t>
         </is>
       </c>
     </row>
